--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -11290,12 +11290,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -11368,40 +11368,185 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>vancomycin-resistant-staphylococcus-aureus-infection</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>万古霉素耐药金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW74" t="inlineStr">
+      <c r="AW75" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
+      <c r="AX75" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr">
+      <c r="AY75" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
+      <c r="AZ75" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA74" t="inlineStr">
+      <c r="BA75" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB74" t="inlineStr">
+      <c r="BB75" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC74" t="inlineStr">
+      <c r="BC75" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -11523,7 +11668,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -11533,7 +11678,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -11552,6 +11552,151 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>vancomycin-resistant-staphylococcus-aureus-infection</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>万古霉素耐药金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11585,7 +11730,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11668,7 +11813,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -11678,7 +11823,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -11697,6 +11697,151 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>vancomycin-resistant-staphylococcus-aureus-infection</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>万古霉素耐药金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11730,7 +11875,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11813,7 +11958,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -11823,7 +11968,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -11842,6 +11842,296 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>vancomycin-resistant-staphylococcus-aureus-infection</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>万古霉素耐药金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>vancomycin-resistant-staphylococcus-aureus-infection</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>万古霉素耐药金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11875,7 +12165,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -11958,7 +12248,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -11968,7 +12258,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -12015,12 +12015,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12093,40 +12093,185 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>vancomycin-resistant-staphylococcus-aureus-infection</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>万古霉素耐药金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW79" t="inlineStr">
+      <c r="AW80" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
+      <c r="AX80" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY79" t="inlineStr">
+      <c r="AY80" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
+      <c r="AZ80" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA79" t="inlineStr">
+      <c r="BA80" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB79" t="inlineStr">
+      <c r="BB80" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC79" t="inlineStr">
+      <c r="BC80" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -12248,7 +12393,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -12258,7 +12403,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1217,6 +1227,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1513,6 +1528,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1809,6 +1829,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2105,6 +2130,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2250,6 +2280,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2546,6 +2581,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2842,6 +2882,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3138,6 +3183,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3434,6 +3484,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3579,6 +3634,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3875,6 +3935,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4171,6 +4236,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4467,6 +4537,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4763,6 +4838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4908,6 +4988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5204,6 +5289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5500,6 +5590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5796,6 +5891,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6092,6 +6192,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6237,6 +6342,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6533,6 +6643,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6829,6 +6944,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7125,6 +7245,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7421,6 +7546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7717,6 +7847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7862,6 +7997,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8152,6 +8292,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8442,6 +8587,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8732,6 +8882,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9022,6 +9177,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9167,6 +9327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9457,6 +9622,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9747,6 +9917,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10037,6 +10212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10327,6 +10507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10617,6 +10802,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11487,6 +11677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12210,6 +12405,11 @@
       <c r="S80" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">

--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -12477,6 +12477,151 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>vancomycin-resistant-staphylococcus-aureus-infection</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>万古霉素耐药金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12510,7 +12655,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12738,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -12603,7 +12748,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -915,6 +915,9 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
@@ -926,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -933,26 +941,30 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1216,6 +1228,9 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
@@ -1227,6 +1242,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1234,26 +1254,30 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1517,6 +1541,9 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
@@ -1528,6 +1555,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1535,26 +1567,30 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1818,6 +1854,9 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
@@ -1829,6 +1868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1836,26 +1880,30 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2119,6 +2167,9 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
@@ -2130,6 +2181,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2137,26 +2193,30 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2570,6 +2630,9 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
@@ -2581,6 +2644,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2588,26 +2656,30 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -2871,6 +2943,9 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
@@ -2882,6 +2957,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2889,26 +2969,30 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3172,6 +3256,9 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
@@ -3183,6 +3270,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3190,26 +3282,30 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -3473,6 +3569,9 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
@@ -3484,6 +3583,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3491,26 +3595,30 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -3924,6 +4032,9 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
@@ -3935,6 +4046,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3942,26 +4058,30 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4225,6 +4345,9 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
@@ -4236,6 +4359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4243,26 +4371,30 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -4526,6 +4658,9 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
@@ -4537,6 +4672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4544,26 +4684,30 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -4827,6 +4971,9 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
@@ -4838,6 +4985,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4845,26 +4997,30 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -5278,6 +5434,9 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
@@ -5289,6 +5448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5296,26 +5460,30 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -5579,6 +5747,9 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
@@ -5590,6 +5761,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5597,26 +5773,30 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -5880,6 +6060,9 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
@@ -5891,6 +6074,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5898,26 +6086,30 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -6181,6 +6373,9 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
@@ -6192,6 +6387,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6199,26 +6399,30 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -6632,6 +6836,9 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
@@ -6643,6 +6850,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6650,26 +6862,30 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -6933,6 +7149,9 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
@@ -6944,6 +7163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6951,26 +7175,30 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -7234,6 +7462,9 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
@@ -7245,6 +7476,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7252,26 +7488,30 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -7535,6 +7775,9 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
@@ -7546,6 +7789,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7553,26 +7801,30 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -7836,6 +8088,9 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
@@ -7847,6 +8102,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7854,26 +8114,30 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -8284,6 +8548,9 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -8292,6 +8559,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8299,26 +8571,30 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -8579,6 +8855,9 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -8587,6 +8866,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8594,26 +8878,30 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -8874,6 +9162,9 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -8882,6 +9173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8889,26 +9185,30 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -9169,6 +9469,9 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9177,6 +9480,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9184,26 +9492,30 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -9614,6 +9926,9 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -9622,6 +9937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9629,26 +9949,30 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -9909,6 +10233,9 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -9917,6 +10244,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9924,26 +10256,30 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -10204,6 +10540,9 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10212,6 +10551,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10219,26 +10563,30 @@
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -10499,6 +10847,9 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10507,6 +10858,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10514,26 +10870,30 @@
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>HOLD_US_a18866fbfc470fd7a2e385ee9f24</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
